--- a/Benchmarks/Water Chemistry/Total Phosphorus/TP_Spearmans_Matrix.xlsx
+++ b/Benchmarks/Water Chemistry/Total Phosphorus/TP_Spearmans_Matrix.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://stateoforegon-my.sharepoint.com/personal/adam_thompson_deq_oregon_gov/Documents/Documents/BioMonORDEQ/Benchmarks/Water Chemistry/Total Phosphorus/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://stateoforegon-my.sharepoint.com/personal/sabine_berzins_deq_oregon_gov/Documents/Documents/BioMonORDEQ/Benchmarks/Water Chemistry/Total Phosphorus/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_7B187FC08F79A8D366075C52F37BD2726ACBE6B2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0362A367-D26C-43AD-8D22-0EFE67747804}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_7B187FC08F79A8D366075C52F37BD2726ACBE6B2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2E1EFD42-5132-47D5-ADA2-99FA8BADC059}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -785,6 +785,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C450"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="2" width="30" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.6640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
